--- a/RRL_Datenbasis_bereinigt.xlsx
+++ b/RRL_Datenbasis_bereinigt.xlsx
@@ -41293,7 +41293,7 @@
       </c>
       <c r="C122" s="4" t="inlineStr">
         <is>
-          <t>KIBACHA</t>
+          <t>JOHANSSONICK</t>
         </is>
       </c>
       <c r="D122" s="4" t="n">
